--- a/ModExcel/Z装备配置表.xlsx
+++ b/ModExcel/Z装备配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\survivors\data\Mod表格数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0516D3F3-0410-4A87-A282-3D22C72187D2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4F74C0-67A6-4F34-96A5-B9BECDD81794}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="装备表" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="1687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2587" uniqueCount="1728">
   <si>
     <t>id_i</t>
   </si>
@@ -5438,14 +5438,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>233:75;234:75;219:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>233:20;234:30;219:-99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:702,32,48,305,300,500,715,16,24,517,6,10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6287,10 +6279,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:206,16,124,213,18,36,323,24,36;4:40043</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:101,16,24,102,16,24,103,16,24,306,40,60;4:40045</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6356,6 +6344,162 @@
   </si>
   <si>
     <t>1:204,8,16,226,10,25,311,4,8;4:40086</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:206,16,24,213,18,36,323,24,36;4:40043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正义使者</t>
+  </si>
+  <si>
+    <t>血罗</t>
+  </si>
+  <si>
+    <t>远古诸王之锤</t>
+  </si>
+  <si>
+    <t>剧毒之血</t>
+  </si>
+  <si>
+    <t>青牙</t>
+  </si>
+  <si>
+    <t>多功能刀</t>
+  </si>
+  <si>
+    <t>雷霆结晶</t>
+  </si>
+  <si>
+    <t>古神绷带</t>
+  </si>
+  <si>
+    <t>黑水之赐</t>
+  </si>
+  <si>
+    <t>脓汁之母</t>
+  </si>
+  <si>
+    <t>233:40;234:65;219:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:15;234:18;219:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:23;234:30;219:-50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:12;234:30;219:12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:15;234:23;219:11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:16;234:34;219:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:8;234:15;219:8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:11;234:15;219:18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>640022</t>
+  </si>
+  <si>
+    <t>640023</t>
+  </si>
+  <si>
+    <t>640024</t>
+  </si>
+  <si>
+    <t>640025</t>
+  </si>
+  <si>
+    <t>640026</t>
+  </si>
+  <si>
+    <t>640027</t>
+  </si>
+  <si>
+    <t>640028</t>
+  </si>
+  <si>
+    <t>640029</t>
+  </si>
+  <si>
+    <t>640030</t>
+  </si>
+  <si>
+    <t>640031</t>
+  </si>
+  <si>
+    <t>1:101,25,50,217,12,25,211,20,45,215,20,45;4:40103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:101,15,30,300,50,100,413,30,50;4:40104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:102,15,25,240,5,10,242,5,10;4:40106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:211,30,50,216,30,50,404,1,1,405,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:102,20,35,300,30,55,313,5,8,721,25,50;4:40107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:215,25,50,318,25,50,213,10,20;2:1009;3:10036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:303,100,200;2:2001;3:10037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:103,20,45,104,-15,-10,213,20,40,317,20,40;2:2002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:101,-15,-10,216,20,40,319,20,40,242,5,10;2:2003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10310</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10704</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10701</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5508</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233:22;234:53;219:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:101,20,35,304,20,35,432,20,35;4:40105</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7522,8 +7666,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F793BD73-4E02-4E2F-96CF-DB54567237CD}" name="表1" displayName="表1" ref="E4:AI464" tableType="xml" totalsRowShown="0" dataDxfId="45" connectionId="16">
-  <autoFilter ref="E4:AI464" xr:uid="{B659AF48-02A7-4ABB-84D4-0285A1C2CE4E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F793BD73-4E02-4E2F-96CF-DB54567237CD}" name="表1" displayName="表1" ref="E4:AI474" tableType="xml" totalsRowShown="0" dataDxfId="45" connectionId="16">
+  <autoFilter ref="E4:AI474" xr:uid="{B659AF48-02A7-4ABB-84D4-0285A1C2CE4E}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{75FA260E-D26F-4AD8-A590-0BA97429F5E5}" uniqueName="id_i" name="id_i" dataDxfId="44">
       <xmlColumnPr mapId="45" xpath="/root/data/id_i" xmlDataType="integer"/>
@@ -7950,7 +8094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AI464"/>
+  <dimension ref="A1:AI474"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.125" customWidth="1"/>
@@ -8068,7 +8212,7 @@
         <v>46</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>6</v>
@@ -8163,7 +8307,7 @@
         <v>48</v>
       </c>
       <c r="AB4" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="AC4" t="s">
         <v>14</v>
@@ -8444,7 +8588,7 @@
         <v>1090101</v>
       </c>
       <c r="AB7" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC7" s="18">
         <v>1001</v>
@@ -8530,7 +8674,7 @@
         <v>1090401</v>
       </c>
       <c r="AB8" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC8" s="18">
         <v>1003</v>
@@ -8616,7 +8760,7 @@
         <v>1092001</v>
       </c>
       <c r="AB9" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC9" s="18">
         <v>1007</v>
@@ -8702,7 +8846,7 @@
         <v>1090501</v>
       </c>
       <c r="AB10" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC10" s="18">
         <v>1001</v>
@@ -8788,7 +8932,7 @@
         <v>1090201</v>
       </c>
       <c r="AB11" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC11" s="18">
         <v>1002</v>
@@ -8874,7 +9018,7 @@
         <v>1091021</v>
       </c>
       <c r="AB12" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC12" s="18">
         <v>1004</v>
@@ -8960,7 +9104,7 @@
         <v>1092101</v>
       </c>
       <c r="AB13" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC13" s="18">
         <v>1021</v>
@@ -9046,7 +9190,7 @@
         <v>1091302</v>
       </c>
       <c r="AB14" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC14" s="18">
         <v>1013</v>
@@ -9132,7 +9276,7 @@
         <v>1091701</v>
       </c>
       <c r="AB15" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC15" s="18">
         <v>1017</v>
@@ -9218,7 +9362,7 @@
         <v>1091002</v>
       </c>
       <c r="AB16" s="18" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="AC16" s="18">
         <v>1010</v>
@@ -9279,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="T17" s="18">
         <v>0</v>
@@ -9386,7 +9530,7 @@
         <v>1091302</v>
       </c>
       <c r="AB18" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC18" s="18">
         <v>1013</v>
@@ -9472,7 +9616,7 @@
         <v>1091302</v>
       </c>
       <c r="AB19" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC19" s="18">
         <v>1013</v>
@@ -9558,7 +9702,7 @@
         <v>1091302</v>
       </c>
       <c r="AB20" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC20" s="18">
         <v>1013</v>
@@ -9644,7 +9788,7 @@
         <v>1091302</v>
       </c>
       <c r="AB21" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC21" s="18">
         <v>1013</v>
@@ -10316,7 +10460,7 @@
         <v>1090101</v>
       </c>
       <c r="AB29" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC29" s="18">
         <v>1001</v>
@@ -10404,7 +10548,7 @@
         <v>1090401</v>
       </c>
       <c r="AB30" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC30" s="18">
         <v>1003</v>
@@ -10492,7 +10636,7 @@
         <v>1092001</v>
       </c>
       <c r="AB31" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC31" s="18">
         <v>1007</v>
@@ -10580,7 +10724,7 @@
         <v>1090501</v>
       </c>
       <c r="AB32" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC32" s="18">
         <v>1001</v>
@@ -10668,7 +10812,7 @@
         <v>1090201</v>
       </c>
       <c r="AB33" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC33" s="18">
         <v>1002</v>
@@ -10756,7 +10900,7 @@
         <v>1091021</v>
       </c>
       <c r="AB34" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC34" s="18">
         <v>1004</v>
@@ -10844,7 +10988,7 @@
         <v>1092101</v>
       </c>
       <c r="AB35" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC35" s="18">
         <v>1021</v>
@@ -10932,7 +11076,7 @@
         <v>1091302</v>
       </c>
       <c r="AB36" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC36" s="18">
         <v>1013</v>
@@ -11020,7 +11164,7 @@
         <v>1091701</v>
       </c>
       <c r="AB37" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC37" s="18">
         <v>1017</v>
@@ -11108,7 +11252,7 @@
         <v>1091002</v>
       </c>
       <c r="AB38" s="18" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="AC38" s="18">
         <v>1010</v>
@@ -11171,7 +11315,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="24" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="T39" s="18">
         <v>0</v>
@@ -11280,7 +11424,7 @@
         <v>1091302</v>
       </c>
       <c r="AB40" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC40" s="18">
         <v>1013</v>
@@ -11368,7 +11512,7 @@
         <v>1091302</v>
       </c>
       <c r="AB41" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC41" s="18">
         <v>1013</v>
@@ -11456,7 +11600,7 @@
         <v>1091302</v>
       </c>
       <c r="AB42" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC42" s="18">
         <v>1013</v>
@@ -11544,7 +11688,7 @@
         <v>1091302</v>
       </c>
       <c r="AB43" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC43" s="18">
         <v>1013</v>
@@ -12226,7 +12370,7 @@
         <v>1090101</v>
       </c>
       <c r="AB51" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC51" s="18">
         <v>1001</v>
@@ -12314,7 +12458,7 @@
         <v>1090401</v>
       </c>
       <c r="AB52" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC52" s="18">
         <v>1003</v>
@@ -12402,7 +12546,7 @@
         <v>1092001</v>
       </c>
       <c r="AB53" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC53" s="18">
         <v>1007</v>
@@ -12490,7 +12634,7 @@
         <v>1090501</v>
       </c>
       <c r="AB54" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC54" s="18">
         <v>1001</v>
@@ -12578,7 +12722,7 @@
         <v>1090201</v>
       </c>
       <c r="AB55" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC55" s="18">
         <v>1002</v>
@@ -12666,7 +12810,7 @@
         <v>1091021</v>
       </c>
       <c r="AB56" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC56" s="18">
         <v>1004</v>
@@ -12754,7 +12898,7 @@
         <v>1092101</v>
       </c>
       <c r="AB57" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC57" s="18">
         <v>1021</v>
@@ -12842,7 +12986,7 @@
         <v>1091302</v>
       </c>
       <c r="AB58" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC58" s="18">
         <v>1013</v>
@@ -12930,7 +13074,7 @@
         <v>1091701</v>
       </c>
       <c r="AB59" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC59" s="18">
         <v>1017</v>
@@ -13018,7 +13162,7 @@
         <v>1091002</v>
       </c>
       <c r="AB60" s="18" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="AC60" s="18">
         <v>1010</v>
@@ -13081,7 +13225,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="24" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="T61" s="18">
         <v>0</v>
@@ -13190,7 +13334,7 @@
         <v>1091302</v>
       </c>
       <c r="AB62" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC62" s="18">
         <v>1013</v>
@@ -13278,7 +13422,7 @@
         <v>1091302</v>
       </c>
       <c r="AB63" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC63" s="18">
         <v>1013</v>
@@ -13366,7 +13510,7 @@
         <v>1091302</v>
       </c>
       <c r="AB64" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC64" s="18">
         <v>1013</v>
@@ -13454,7 +13598,7 @@
         <v>1091302</v>
       </c>
       <c r="AB65" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC65" s="18">
         <v>1013</v>
@@ -14136,7 +14280,7 @@
         <v>1090101</v>
       </c>
       <c r="AB73" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC73" s="18">
         <v>1001</v>
@@ -14224,7 +14368,7 @@
         <v>1090401</v>
       </c>
       <c r="AB74" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC74" s="18">
         <v>1003</v>
@@ -14312,7 +14456,7 @@
         <v>1092001</v>
       </c>
       <c r="AB75" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC75" s="18">
         <v>1007</v>
@@ -14400,7 +14544,7 @@
         <v>1090501</v>
       </c>
       <c r="AB76" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC76" s="18">
         <v>1001</v>
@@ -14488,7 +14632,7 @@
         <v>1090201</v>
       </c>
       <c r="AB77" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC77" s="18">
         <v>1002</v>
@@ -14576,7 +14720,7 @@
         <v>1091021</v>
       </c>
       <c r="AB78" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC78" s="18">
         <v>1004</v>
@@ -14664,7 +14808,7 @@
         <v>1092101</v>
       </c>
       <c r="AB79" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC79" s="18">
         <v>1021</v>
@@ -14752,7 +14896,7 @@
         <v>1091302</v>
       </c>
       <c r="AB80" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC80" s="18">
         <v>1013</v>
@@ -14840,7 +14984,7 @@
         <v>1091701</v>
       </c>
       <c r="AB81" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC81" s="18">
         <v>1017</v>
@@ -14928,7 +15072,7 @@
         <v>1091002</v>
       </c>
       <c r="AB82" s="18" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="AC82" s="18">
         <v>1010</v>
@@ -14991,7 +15135,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="24" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="T83" s="18">
         <v>0</v>
@@ -15100,7 +15244,7 @@
         <v>1091302</v>
       </c>
       <c r="AB84" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC84" s="18">
         <v>1013</v>
@@ -15188,7 +15332,7 @@
         <v>1091302</v>
       </c>
       <c r="AB85" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC85" s="18">
         <v>1013</v>
@@ -15276,7 +15420,7 @@
         <v>1091302</v>
       </c>
       <c r="AB86" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC86" s="18">
         <v>1013</v>
@@ -15364,7 +15508,7 @@
         <v>1091302</v>
       </c>
       <c r="AB87" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC87" s="18">
         <v>1013</v>
@@ -16048,7 +16192,7 @@
         <v>1091302</v>
       </c>
       <c r="AB95" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC95" s="18">
         <v>1013</v>
@@ -16147,7 +16291,7 @@
         <v>1091302</v>
       </c>
       <c r="AB96" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC96" s="49">
         <v>1013</v>
@@ -16245,7 +16389,7 @@
         <v>1091302</v>
       </c>
       <c r="AB97" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC97" s="18">
         <v>1013</v>
@@ -16341,7 +16485,7 @@
         <v>1091302</v>
       </c>
       <c r="AB98" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC98" s="18">
         <v>1013</v>
@@ -16440,7 +16584,7 @@
         <v>1091302</v>
       </c>
       <c r="AB99" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC99" s="49">
         <v>1013</v>
@@ -16538,7 +16682,7 @@
         <v>1091302</v>
       </c>
       <c r="AB100" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC100" s="18">
         <v>1013</v>
@@ -16634,7 +16778,7 @@
         <v>1091302</v>
       </c>
       <c r="AB101" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC101" s="18">
         <v>1013</v>
@@ -16732,7 +16876,7 @@
         <v>1090101</v>
       </c>
       <c r="AB102" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC102" s="18">
         <v>1001</v>
@@ -16830,7 +16974,7 @@
         <v>1090101</v>
       </c>
       <c r="AB103" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC103" s="18">
         <v>1001</v>
@@ -16928,7 +17072,7 @@
         <v>1090101</v>
       </c>
       <c r="AB104" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC104" s="18">
         <v>1001</v>
@@ -17026,7 +17170,7 @@
         <v>1090101</v>
       </c>
       <c r="AB105" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC105" s="18">
         <v>1001</v>
@@ -17124,7 +17268,7 @@
         <v>1090101</v>
       </c>
       <c r="AB106" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC106" s="18">
         <v>1001</v>
@@ -17222,7 +17366,7 @@
         <v>1090501</v>
       </c>
       <c r="AB107" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC107" s="18">
         <v>1001</v>
@@ -17320,7 +17464,7 @@
         <v>1090501</v>
       </c>
       <c r="AB108" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC108" s="18">
         <v>1001</v>
@@ -17418,7 +17562,7 @@
         <v>1090501</v>
       </c>
       <c r="AB109" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC109" s="18">
         <v>1001</v>
@@ -17516,7 +17660,7 @@
         <v>1090501</v>
       </c>
       <c r="AB110" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC110" s="18">
         <v>1001</v>
@@ -17614,7 +17758,7 @@
         <v>1090501</v>
       </c>
       <c r="AB111" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC111" s="18">
         <v>1001</v>
@@ -17712,7 +17856,7 @@
         <v>1090401</v>
       </c>
       <c r="AB112" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC112" s="18">
         <v>1003</v>
@@ -17810,7 +17954,7 @@
         <v>1090401</v>
       </c>
       <c r="AB113" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC113" s="18">
         <v>1003</v>
@@ -17908,7 +18052,7 @@
         <v>1090401</v>
       </c>
       <c r="AB114" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC114" s="18">
         <v>1003</v>
@@ -18006,7 +18150,7 @@
         <v>1091021</v>
       </c>
       <c r="AB115" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC115" s="18">
         <v>1004</v>
@@ -18104,7 +18248,7 @@
         <v>1091021</v>
       </c>
       <c r="AB116" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC116" s="18">
         <v>1004</v>
@@ -18202,7 +18346,7 @@
         <v>1091021</v>
       </c>
       <c r="AB117" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC117" s="18">
         <v>1004</v>
@@ -18300,7 +18444,7 @@
         <v>1092101</v>
       </c>
       <c r="AB118" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC118" s="18">
         <v>1021</v>
@@ -18398,7 +18542,7 @@
         <v>1090201</v>
       </c>
       <c r="AB119" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC119" s="18">
         <v>1002</v>
@@ -18496,7 +18640,7 @@
         <v>1090201</v>
       </c>
       <c r="AB120" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC120" s="18">
         <v>1002</v>
@@ -18594,7 +18738,7 @@
         <v>1090201</v>
       </c>
       <c r="AB121" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC121" s="18">
         <v>1002</v>
@@ -18692,7 +18836,7 @@
         <v>1090201</v>
       </c>
       <c r="AB122" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC122" s="18">
         <v>1002</v>
@@ -18790,7 +18934,7 @@
         <v>1090201</v>
       </c>
       <c r="AB123" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC123" s="18">
         <v>1002</v>
@@ -18890,7 +19034,7 @@
         <v>1091002</v>
       </c>
       <c r="AB124" s="18" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="AC124" s="18">
         <v>1010</v>
@@ -18985,7 +19129,7 @@
         <v>1091002</v>
       </c>
       <c r="AB125" s="18" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="AC125" s="18">
         <v>1010</v>
@@ -19083,7 +19227,7 @@
         <v>1091701</v>
       </c>
       <c r="AB126" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC126" s="18">
         <v>1017</v>
@@ -19181,7 +19325,7 @@
         <v>1091701</v>
       </c>
       <c r="AB127" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC127" s="18">
         <v>1017</v>
@@ -19279,7 +19423,7 @@
         <v>1091701</v>
       </c>
       <c r="AB128" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC128" s="18">
         <v>1017</v>
@@ -19377,7 +19521,7 @@
         <v>1091701</v>
       </c>
       <c r="AB129" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC129" s="18">
         <v>1017</v>
@@ -19475,7 +19619,7 @@
         <v>1091701</v>
       </c>
       <c r="AB130" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC130" s="18">
         <v>1017</v>
@@ -19573,7 +19717,7 @@
         <v>1091701</v>
       </c>
       <c r="AB131" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC131" s="18">
         <v>1017</v>
@@ -19671,7 +19815,7 @@
         <v>1091701</v>
       </c>
       <c r="AB132" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC132" s="18">
         <v>1017</v>
@@ -19745,10 +19889,10 @@
         <v>636</v>
       </c>
       <c r="T133" s="24" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="U133" s="46" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="V133" s="24">
         <v>101</v>
@@ -19769,7 +19913,7 @@
         <v>1091701</v>
       </c>
       <c r="AB133" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC133" s="18">
         <v>1017</v>
@@ -19867,7 +20011,7 @@
         <v>1091701</v>
       </c>
       <c r="AB134" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC134" s="18">
         <v>1017</v>
@@ -19965,7 +20109,7 @@
         <v>1091701</v>
       </c>
       <c r="AB135" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC135" s="18">
         <v>1017</v>
@@ -20036,13 +20180,13 @@
         <v>0</v>
       </c>
       <c r="S136" s="24" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="T136" s="24" t="s">
         <v>310</v>
       </c>
       <c r="U136" s="46" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="V136" s="24">
         <v>101</v>
@@ -20130,7 +20274,7 @@
         <v>0</v>
       </c>
       <c r="S137" s="24" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="T137" s="24">
         <v>14237</v>
@@ -20224,7 +20368,7 @@
         <v>0</v>
       </c>
       <c r="S138" s="24" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="T138" s="24">
         <v>14238</v>
@@ -20318,7 +20462,7 @@
         <v>0</v>
       </c>
       <c r="S139" s="24" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="T139" s="24">
         <v>14239</v>
@@ -20412,13 +20556,13 @@
         <v>0</v>
       </c>
       <c r="S140" s="24" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="T140" s="24" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="U140" s="46" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="V140" s="24">
         <v>101</v>
@@ -20506,10 +20650,10 @@
         <v>0</v>
       </c>
       <c r="S141" s="24" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="T141" s="24" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="U141" s="46" t="s">
         <v>1274</v>
@@ -20600,7 +20744,7 @@
         <v>0</v>
       </c>
       <c r="S142" s="24" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="T142" s="24">
         <v>14242</v>
@@ -20694,13 +20838,13 @@
         <v>0</v>
       </c>
       <c r="S143" s="24" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="T143" s="24" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="U143" s="46" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="V143" s="24">
         <v>101</v>
@@ -20788,7 +20932,7 @@
         <v>0</v>
       </c>
       <c r="S144" s="24" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="T144" s="24">
         <v>14244</v>
@@ -20882,7 +21026,7 @@
         <v>0</v>
       </c>
       <c r="S145" s="24" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="T145" s="24">
         <v>14245</v>
@@ -21270,7 +21414,7 @@
         <v>14249</v>
       </c>
       <c r="U149" s="46" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="V149" s="24">
         <v>101</v>
@@ -22407,7 +22551,7 @@
         <v>14261</v>
       </c>
       <c r="U161" s="46" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="V161" s="24">
         <v>101</v>
@@ -23945,7 +24089,7 @@
         <v>14277</v>
       </c>
       <c r="U177" s="46" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="V177" s="24">
         <v>101</v>
@@ -26347,7 +26491,7 @@
         <v>315</v>
       </c>
       <c r="U202" s="46" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="V202" s="24">
         <v>101</v>
@@ -27573,7 +27717,7 @@
         <v>14318</v>
       </c>
       <c r="U215" s="46" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="V215" s="24">
         <v>101</v>
@@ -30395,7 +30539,7 @@
         <v>14349</v>
       </c>
       <c r="U245" s="46" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="V245" s="24">
         <v>101</v>
@@ -32479,7 +32623,7 @@
         <v>1091302</v>
       </c>
       <c r="AB267" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC267" s="18">
         <v>1013</v>
@@ -32572,7 +32716,7 @@
         <v>1091302</v>
       </c>
       <c r="AB268" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC268" s="18">
         <v>1013</v>
@@ -34716,7 +34860,7 @@
         <v>1115</v>
       </c>
       <c r="U292" s="46" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="V292" s="24">
         <v>101</v>
@@ -35616,7 +35760,7 @@
         <v>14406</v>
       </c>
       <c r="U302" s="46" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="V302" s="24">
         <v>101</v>
@@ -35725,7 +35869,7 @@
         <v>1091302</v>
       </c>
       <c r="AB303" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC303" s="18">
         <v>1013</v>
@@ -35817,7 +35961,7 @@
         <v>1090501</v>
       </c>
       <c r="AB304" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC304" s="18">
         <v>1001</v>
@@ -35909,7 +36053,7 @@
         <v>1091701</v>
       </c>
       <c r="AB305" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC305" s="18">
         <v>1017</v>
@@ -35999,7 +36143,7 @@
         <v>1091302</v>
       </c>
       <c r="AB306" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC306" s="18">
         <v>1013</v>
@@ -36091,7 +36235,7 @@
         <v>1091021</v>
       </c>
       <c r="AB307" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC307" s="18">
         <v>1004</v>
@@ -36181,7 +36325,7 @@
         <v>1091302</v>
       </c>
       <c r="AB308" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC308" s="18">
         <v>1013</v>
@@ -36273,7 +36417,7 @@
         <v>1091701</v>
       </c>
       <c r="AB309" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC309" s="18">
         <v>1017</v>
@@ -37462,7 +37606,7 @@
         <v>1091302</v>
       </c>
       <c r="AB322" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC322" s="18">
         <v>1013</v>
@@ -37984,7 +38128,7 @@
         <v>1090201</v>
       </c>
       <c r="AB328" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC328" s="18">
         <v>1002</v>
@@ -38224,10 +38368,10 @@
         <v>681</v>
       </c>
       <c r="T331" s="24" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="U331" s="46" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="V331" s="24">
         <v>2301</v>
@@ -38506,7 +38650,7 @@
         <v>1091302</v>
       </c>
       <c r="AB334" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC334" s="18">
         <v>1013</v>
@@ -39028,7 +39172,7 @@
         <v>1090101</v>
       </c>
       <c r="AB340" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC340" s="18">
         <v>1001</v>
@@ -39118,7 +39262,7 @@
         <v>1090401</v>
       </c>
       <c r="AB341" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC341" s="18">
         <v>1003</v>
@@ -39480,7 +39624,7 @@
     </row>
     <row r="346" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B346" s="72" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="C346" s="60" t="s">
         <v>479</v>
@@ -39554,7 +39698,7 @@
         <v>1091701</v>
       </c>
       <c r="AB346" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC346" s="18">
         <v>1017</v>
@@ -40002,7 +40146,7 @@
     </row>
     <row r="352" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B352" s="73" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="C352" s="61" t="s">
         <v>490</v>
@@ -40229,7 +40373,7 @@
         <v>495</v>
       </c>
       <c r="U354" s="46" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="V354" s="18">
         <v>2301</v>
@@ -40520,7 +40664,7 @@
     </row>
     <row r="358" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B358" s="72" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="C358" s="60" t="s">
         <v>501</v>
@@ -40575,7 +40719,7 @@
         <v>535</v>
       </c>
       <c r="U358" s="46" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="V358" s="18">
         <v>801</v>
@@ -40594,7 +40738,7 @@
         <v>1091302</v>
       </c>
       <c r="AB358" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC358" s="36">
         <v>1013</v>
@@ -41042,7 +41186,7 @@
     </row>
     <row r="364" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B364" s="73" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C364" s="61" t="s">
         <v>512</v>
@@ -41116,7 +41260,7 @@
         <v>1091302</v>
       </c>
       <c r="AB364" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC364" s="39">
         <v>1013</v>
@@ -42575,7 +42719,7 @@
         <v>1370</v>
       </c>
       <c r="U381" s="46" t="s">
-        <v>1669</v>
+        <v>1684</v>
       </c>
       <c r="V381" s="24">
         <v>101</v>
@@ -42594,7 +42738,7 @@
         <v>1091302</v>
       </c>
       <c r="AB381" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC381" s="18">
         <v>1013</v>
@@ -42753,7 +42897,7 @@
         <v>1372</v>
       </c>
       <c r="U383" s="46" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="V383" s="24">
         <v>101</v>
@@ -42925,7 +43069,7 @@
         <v>1374</v>
       </c>
       <c r="U385" s="46" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="V385" s="24">
         <v>101</v>
@@ -43118,7 +43262,7 @@
         <v>1090101</v>
       </c>
       <c r="AB387" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC387" s="18">
         <v>1001</v>
@@ -43363,7 +43507,7 @@
         <v>1380</v>
       </c>
       <c r="U390" s="46" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="V390" s="24">
         <v>101</v>
@@ -43449,7 +43593,7 @@
         <v>1381</v>
       </c>
       <c r="U391" s="46" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="V391" s="24">
         <v>101</v>
@@ -43535,7 +43679,7 @@
         <v>1382</v>
       </c>
       <c r="U392" s="46" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="V392" s="24">
         <v>101</v>
@@ -43642,7 +43786,7 @@
         <v>1091701</v>
       </c>
       <c r="AB393" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC393" s="18">
         <v>1017</v>
@@ -44059,7 +44203,7 @@
         <v>1389</v>
       </c>
       <c r="U398" s="46" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="V398" s="24">
         <v>101</v>
@@ -44577,7 +44721,7 @@
         <v>1396</v>
       </c>
       <c r="U404" s="46" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="V404" s="24">
         <v>101</v>
@@ -44608,13 +44752,13 @@
     </row>
     <row r="405" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B405" s="64" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="C405" s="62" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="D405" s="44" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="E405" s="18">
         <v>30084</v>
@@ -44626,7 +44770,7 @@
         <v>600190</v>
       </c>
       <c r="H405" s="24" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="I405" s="18">
         <v>2</v>
@@ -44659,13 +44803,13 @@
         <v>0</v>
       </c>
       <c r="S405" s="24" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="T405" s="24" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="U405" s="46" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="V405" s="24">
         <v>101</v>
@@ -44701,7 +44845,7 @@
     <row r="406" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B406" s="65"/>
       <c r="C406" s="62" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="D406" s="44" t="s">
         <v>1364</v>
@@ -44716,7 +44860,7 @@
         <v>600191</v>
       </c>
       <c r="H406" s="24" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I406" s="18">
         <v>2</v>
@@ -44749,13 +44893,13 @@
         <v>0</v>
       </c>
       <c r="S406" s="24" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="T406" s="24" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="U406" s="46" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="V406" s="24">
         <v>101</v>
@@ -44787,7 +44931,7 @@
     <row r="407" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B407" s="65"/>
       <c r="C407" s="62" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D407" s="44" t="s">
         <v>266</v>
@@ -44802,7 +44946,7 @@
         <v>600192</v>
       </c>
       <c r="H407" s="24" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="I407" s="18">
         <v>2</v>
@@ -44835,13 +44979,13 @@
         <v>0</v>
       </c>
       <c r="S407" s="24" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="T407" s="24" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="U407" s="46" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="V407" s="24">
         <v>101</v>
@@ -44873,7 +45017,7 @@
     <row r="408" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B408" s="65"/>
       <c r="C408" s="62" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="D408" s="44" t="s">
         <v>1366</v>
@@ -44888,7 +45032,7 @@
         <v>600193</v>
       </c>
       <c r="H408" s="24" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="I408" s="18">
         <v>2</v>
@@ -44921,13 +45065,13 @@
         <v>0</v>
       </c>
       <c r="S408" s="24" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="T408" s="24" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="U408" s="46" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
       <c r="V408" s="24">
         <v>101</v>
@@ -44959,10 +45103,10 @@
     <row r="409" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B409" s="65"/>
       <c r="C409" s="62" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="D409" s="44" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="E409" s="18">
         <v>30088</v>
@@ -45007,13 +45151,13 @@
         <v>0</v>
       </c>
       <c r="S409" s="24" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="T409" s="24" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="U409" s="46" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="V409" s="24">
         <v>101</v>
@@ -45045,7 +45189,7 @@
     <row r="410" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B410" s="66"/>
       <c r="C410" s="62" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="D410" s="44" t="s">
         <v>270</v>
@@ -45060,7 +45204,7 @@
         <v>600195</v>
       </c>
       <c r="H410" s="24" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="I410" s="18">
         <v>1</v>
@@ -45096,10 +45240,10 @@
         <v>85</v>
       </c>
       <c r="T410" s="24" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="U410" s="46" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="V410" s="24">
         <v>101</v>
@@ -45130,13 +45274,13 @@
     </row>
     <row r="411" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B411" s="67" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="C411" s="63" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="D411" s="48" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="E411" s="18">
         <v>30090</v>
@@ -45148,7 +45292,7 @@
         <v>600203</v>
       </c>
       <c r="H411" s="24" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="I411" s="18">
         <v>2</v>
@@ -45181,13 +45325,13 @@
         <v>0</v>
       </c>
       <c r="S411" s="24" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="T411" s="24" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="U411" s="46" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="V411" s="24">
         <v>101</v>
@@ -45223,7 +45367,7 @@
     <row r="412" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B412" s="68"/>
       <c r="C412" s="63" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="D412" s="48" t="s">
         <v>1364</v>
@@ -45238,7 +45382,7 @@
         <v>600204</v>
       </c>
       <c r="H412" s="24" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="I412" s="18">
         <v>2</v>
@@ -45271,13 +45415,13 @@
         <v>0</v>
       </c>
       <c r="S412" s="24" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="T412" s="24" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="U412" s="46" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="V412" s="24">
         <v>101</v>
@@ -45309,7 +45453,7 @@
     <row r="413" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B413" s="68"/>
       <c r="C413" s="63" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="D413" s="48" t="s">
         <v>1365</v>
@@ -45357,13 +45501,13 @@
         <v>0</v>
       </c>
       <c r="S413" s="24" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="T413" s="24" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="U413" s="46" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="V413" s="24">
         <v>101</v>
@@ -45395,7 +45539,7 @@
     <row r="414" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B414" s="68"/>
       <c r="C414" s="63" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="D414" s="48" t="s">
         <v>1366</v>
@@ -45443,13 +45587,13 @@
         <v>0</v>
       </c>
       <c r="S414" s="24" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="T414" s="24" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="U414" s="46" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="V414" s="24">
         <v>101</v>
@@ -45481,7 +45625,7 @@
     <row r="415" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B415" s="68"/>
       <c r="C415" s="63" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D415" s="48" t="s">
         <v>1367</v>
@@ -45529,13 +45673,13 @@
         <v>0</v>
       </c>
       <c r="S415" s="24" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="T415" s="24" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="U415" s="46" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="V415" s="24">
         <v>101</v>
@@ -45567,7 +45711,7 @@
     <row r="416" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B416" s="69"/>
       <c r="C416" s="63" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="D416" s="48" t="s">
         <v>269</v>
@@ -45615,13 +45759,13 @@
         <v>0</v>
       </c>
       <c r="S416" s="24" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="T416" s="24" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="U416" s="46" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="V416" s="24">
         <v>101</v>
@@ -45652,10 +45796,10 @@
     </row>
     <row r="417" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B417" s="64" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="C417" s="62" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="D417" s="44" t="s">
         <v>25</v>
@@ -45703,13 +45847,13 @@
         <v>0</v>
       </c>
       <c r="S417" s="24" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="T417" s="24" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="U417" s="46" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="V417" s="24">
         <v>101</v>
@@ -45728,7 +45872,7 @@
         <v>1090201</v>
       </c>
       <c r="AB417" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC417" s="18">
         <v>1002</v>
@@ -45747,7 +45891,7 @@
     <row r="418" spans="2:35" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B418" s="65"/>
       <c r="C418" s="62" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="D418" s="44" t="s">
         <v>1364</v>
@@ -45795,13 +45939,13 @@
         <v>0</v>
       </c>
       <c r="S418" s="24" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="T418" s="24" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="U418" s="46" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="V418" s="24">
         <v>101</v>
@@ -45833,7 +45977,7 @@
     <row r="419" spans="2:35" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B419" s="65"/>
       <c r="C419" s="62" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="D419" s="44" t="s">
         <v>1365</v>
@@ -45848,7 +45992,7 @@
         <v>600218</v>
       </c>
       <c r="H419" s="24" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="I419" s="18">
         <v>2</v>
@@ -45881,13 +46025,13 @@
         <v>0</v>
       </c>
       <c r="S419" s="24" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="T419" s="24" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="U419" s="46" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="V419" s="24">
         <v>101</v>
@@ -45919,7 +46063,7 @@
     <row r="420" spans="2:35" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B420" s="65"/>
       <c r="C420" s="62" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="D420" s="44" t="s">
         <v>1366</v>
@@ -45934,7 +46078,7 @@
         <v>600219</v>
       </c>
       <c r="H420" s="24" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="I420" s="18">
         <v>2</v>
@@ -45967,13 +46111,13 @@
         <v>0</v>
       </c>
       <c r="S420" s="24" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="T420" s="24" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="U420" s="46" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="V420" s="24">
         <v>101</v>
@@ -46005,7 +46149,7 @@
     <row r="421" spans="2:35" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B421" s="65"/>
       <c r="C421" s="62" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="D421" s="44" t="s">
         <v>1367</v>
@@ -46020,7 +46164,7 @@
         <v>600220</v>
       </c>
       <c r="H421" s="24" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="I421" s="18">
         <v>2</v>
@@ -46053,13 +46197,13 @@
         <v>0</v>
       </c>
       <c r="S421" s="24" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="T421" s="24" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="U421" s="46" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="V421" s="24">
         <v>101</v>
@@ -46091,7 +46235,7 @@
     <row r="422" spans="2:35" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B422" s="66"/>
       <c r="C422" s="62" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="D422" s="44" t="s">
         <v>271</v>
@@ -46142,10 +46286,10 @@
         <v>85</v>
       </c>
       <c r="T422" s="24" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="U422" s="46" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
       <c r="V422" s="24">
         <v>101</v>
@@ -46176,10 +46320,10 @@
     </row>
     <row r="423" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B423" s="67" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C423" s="59" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="D423" s="17" t="s">
         <v>24</v>
@@ -46194,7 +46338,7 @@
         <v>600229</v>
       </c>
       <c r="H423" s="24" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="I423" s="18">
         <v>1</v>
@@ -46227,13 +46371,13 @@
         <v>0</v>
       </c>
       <c r="S423" s="24" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="T423" s="24" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="U423" s="46" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="V423" s="24">
         <v>101</v>
@@ -46254,7 +46398,7 @@
         <v>1090501</v>
       </c>
       <c r="AB423" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC423" s="18">
         <v>1001</v>
@@ -46273,7 +46417,7 @@
     <row r="424" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B424" s="68"/>
       <c r="C424" s="59" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="D424" s="17" t="s">
         <v>24</v>
@@ -46288,7 +46432,7 @@
         <v>600230</v>
       </c>
       <c r="H424" s="24" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="I424" s="18">
         <v>1</v>
@@ -46321,13 +46465,13 @@
         <v>0</v>
       </c>
       <c r="S424" s="24" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="T424" s="24" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="U424" s="46" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
       <c r="V424" s="24">
         <v>101</v>
@@ -46348,7 +46492,7 @@
         <v>1090501</v>
       </c>
       <c r="AB424" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC424" s="18">
         <v>1001</v>
@@ -46367,7 +46511,7 @@
     <row r="425" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B425" s="68"/>
       <c r="C425" s="59" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="D425" s="17" t="s">
         <v>1364</v>
@@ -46382,7 +46526,7 @@
         <v>600231</v>
       </c>
       <c r="H425" s="24" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="I425" s="18">
         <v>2</v>
@@ -46415,13 +46559,13 @@
         <v>0</v>
       </c>
       <c r="S425" s="24" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="T425" s="24" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="U425" s="46" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="V425" s="24">
         <v>101</v>
@@ -46453,7 +46597,7 @@
     <row r="426" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B426" s="68"/>
       <c r="C426" s="59" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="D426" s="17" t="s">
         <v>1365</v>
@@ -46501,13 +46645,13 @@
         <v>0</v>
       </c>
       <c r="S426" s="24" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="T426" s="24" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="U426" s="46" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="V426" s="24">
         <v>101</v>
@@ -46539,7 +46683,7 @@
     <row r="427" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B427" s="68"/>
       <c r="C427" s="59" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="D427" s="17" t="s">
         <v>1366</v>
@@ -46554,7 +46698,7 @@
         <v>600233</v>
       </c>
       <c r="H427" s="24" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="I427" s="18">
         <v>2</v>
@@ -46587,13 +46731,13 @@
         <v>0</v>
       </c>
       <c r="S427" s="24" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="T427" s="24" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="U427" s="46" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="V427" s="24">
         <v>101</v>
@@ -46625,7 +46769,7 @@
     <row r="428" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B428" s="69"/>
       <c r="C428" s="59" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="D428" s="17" t="s">
         <v>271</v>
@@ -46676,10 +46820,10 @@
         <v>85</v>
       </c>
       <c r="T428" s="24" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="U428" s="46" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="V428" s="24">
         <v>101</v>
@@ -46710,10 +46854,10 @@
     </row>
     <row r="429" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B429" s="64" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="C429" s="58" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D429" s="35" t="s">
         <v>24</v>
@@ -46728,7 +46872,7 @@
         <v>600242</v>
       </c>
       <c r="H429" s="24" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="I429" s="18">
         <v>1</v>
@@ -46761,13 +46905,13 @@
         <v>0</v>
       </c>
       <c r="S429" s="24" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="T429" s="24" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="U429" s="46" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="V429" s="24">
         <v>101</v>
@@ -46788,7 +46932,7 @@
         <v>1090501</v>
       </c>
       <c r="AB429" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC429" s="18">
         <v>1001</v>
@@ -46807,7 +46951,7 @@
     <row r="430" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B430" s="65"/>
       <c r="C430" s="58" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="D430" s="35" t="s">
         <v>1364</v>
@@ -46822,7 +46966,7 @@
         <v>600243</v>
       </c>
       <c r="H430" s="24" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="I430" s="18">
         <v>2</v>
@@ -46855,13 +46999,13 @@
         <v>0</v>
       </c>
       <c r="S430" s="24" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="T430" s="24" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="U430" s="46" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
       <c r="V430" s="24">
         <v>101</v>
@@ -46893,7 +47037,7 @@
     <row r="431" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B431" s="65"/>
       <c r="C431" s="58" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D431" s="35" t="s">
         <v>1365</v>
@@ -46941,13 +47085,13 @@
         <v>0</v>
       </c>
       <c r="S431" s="24" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="T431" s="24" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="U431" s="46" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="V431" s="24">
         <v>101</v>
@@ -46979,7 +47123,7 @@
     <row r="432" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B432" s="65"/>
       <c r="C432" s="58" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="D432" s="35" t="s">
         <v>1366</v>
@@ -47027,13 +47171,13 @@
         <v>0</v>
       </c>
       <c r="S432" s="24" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="T432" s="24" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="U432" s="46" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="V432" s="24">
         <v>101</v>
@@ -47065,7 +47209,7 @@
     <row r="433" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B433" s="65"/>
       <c r="C433" s="58" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D433" s="35" t="s">
         <v>1367</v>
@@ -47080,7 +47224,7 @@
         <v>600246</v>
       </c>
       <c r="H433" s="24" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="I433" s="18">
         <v>2</v>
@@ -47113,13 +47257,13 @@
         <v>0</v>
       </c>
       <c r="S433" s="24" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="T433" s="24" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="U433" s="46" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="V433" s="24">
         <v>101</v>
@@ -47151,7 +47295,7 @@
     <row r="434" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B434" s="66"/>
       <c r="C434" s="58" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="D434" s="35" t="s">
         <v>271</v>
@@ -47166,7 +47310,7 @@
         <v>600247</v>
       </c>
       <c r="H434" s="24" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="I434" s="18">
         <v>1</v>
@@ -47202,10 +47346,10 @@
         <v>85</v>
       </c>
       <c r="T434" s="24" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="U434" s="46" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="V434" s="24">
         <v>101</v>
@@ -47236,10 +47380,10 @@
     </row>
     <row r="435" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B435" s="67" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="C435" s="59" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D435" s="17" t="s">
         <v>1364</v>
@@ -47254,7 +47398,7 @@
         <v>600255</v>
       </c>
       <c r="H435" s="24" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="I435" s="18">
         <v>2</v>
@@ -47287,13 +47431,13 @@
         <v>0</v>
       </c>
       <c r="S435" s="24" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="T435" s="24" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="U435" s="46" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="V435" s="24">
         <v>101</v>
@@ -47325,7 +47469,7 @@
     <row r="436" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B436" s="68"/>
       <c r="C436" s="59" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D436" s="17" t="s">
         <v>1365</v>
@@ -47340,7 +47484,7 @@
         <v>600256</v>
       </c>
       <c r="H436" s="24" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="I436" s="18">
         <v>2</v>
@@ -47373,13 +47517,13 @@
         <v>0</v>
       </c>
       <c r="S436" s="24" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="T436" s="24" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="U436" s="46" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="V436" s="24">
         <v>101</v>
@@ -47411,7 +47555,7 @@
     <row r="437" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B437" s="68"/>
       <c r="C437" s="59" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D437" s="17" t="s">
         <v>1366</v>
@@ -47459,13 +47603,13 @@
         <v>0</v>
       </c>
       <c r="S437" s="24" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="T437" s="24" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="U437" s="46" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="V437" s="24">
         <v>101</v>
@@ -47497,7 +47641,7 @@
     <row r="438" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B438" s="68"/>
       <c r="C438" s="59" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D438" s="17" t="s">
         <v>269</v>
@@ -47512,7 +47656,7 @@
         <v>600258</v>
       </c>
       <c r="H438" s="24" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I438" s="18">
         <v>2</v>
@@ -47545,13 +47689,13 @@
         <v>0</v>
       </c>
       <c r="S438" s="24" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="T438" s="24" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="U438" s="46" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="V438" s="24">
         <v>101</v>
@@ -47583,7 +47727,7 @@
     <row r="439" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B439" s="68"/>
       <c r="C439" s="59" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D439" s="17" t="s">
         <v>270</v>
@@ -47634,10 +47778,10 @@
         <v>85</v>
       </c>
       <c r="T439" s="24" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="U439" s="46" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="V439" s="24">
         <v>101</v>
@@ -47669,7 +47813,7 @@
     <row r="440" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B440" s="69"/>
       <c r="C440" s="59" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D440" s="17" t="s">
         <v>271</v>
@@ -47720,10 +47864,10 @@
         <v>85</v>
       </c>
       <c r="T440" s="24" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="U440" s="46" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="V440" s="24">
         <v>101</v>
@@ -47757,7 +47901,7 @@
         <v>1179</v>
       </c>
       <c r="C441" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="D441" t="s">
         <v>264</v>
@@ -47828,7 +47972,7 @@
         <v>1090101</v>
       </c>
       <c r="AB441" s="18" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="AC441" s="18">
         <v>1001</v>
@@ -47846,7 +47990,7 @@
     </row>
     <row r="442" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C442" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D442" t="s">
         <v>22</v>
@@ -47917,7 +48061,7 @@
         <v>1090401</v>
       </c>
       <c r="AB442" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC442" s="18">
         <v>1003</v>
@@ -48006,7 +48150,7 @@
         <v>1092001</v>
       </c>
       <c r="AB443" s="18" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="AC443" s="18">
         <v>1007</v>
@@ -48095,7 +48239,7 @@
         <v>1090201</v>
       </c>
       <c r="AB444" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC444" s="18">
         <v>1002</v>
@@ -48184,7 +48328,7 @@
         <v>1091021</v>
       </c>
       <c r="AB445" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC445" s="18">
         <v>1004</v>
@@ -48273,7 +48417,7 @@
         <v>1092101</v>
       </c>
       <c r="AB446" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC446" s="18">
         <v>1021</v>
@@ -48362,7 +48506,7 @@
         <v>1091302</v>
       </c>
       <c r="AB447" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC447" s="18">
         <v>1013</v>
@@ -48451,7 +48595,7 @@
         <v>1091302</v>
       </c>
       <c r="AB448" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC448" s="18">
         <v>1013</v>
@@ -48467,7 +48611,7 @@
       <c r="AH448" s="18"/>
       <c r="AI448" s="18"/>
     </row>
-    <row r="449" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="449" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C449" t="s">
         <v>1198</v>
       </c>
@@ -48540,7 +48684,7 @@
         <v>1091302</v>
       </c>
       <c r="AB449" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC449" s="18">
         <v>1013</v>
@@ -48556,7 +48700,7 @@
       <c r="AH449" s="18"/>
       <c r="AI449" s="18"/>
     </row>
-    <row r="450" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="450" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C450" t="s">
         <v>1201</v>
       </c>
@@ -48629,7 +48773,7 @@
         <v>1091302</v>
       </c>
       <c r="AB450" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC450" s="18">
         <v>1013</v>
@@ -48645,7 +48789,7 @@
       <c r="AH450" s="18"/>
       <c r="AI450" s="18"/>
     </row>
-    <row r="451" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="451" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C451" t="s">
         <v>1204</v>
       </c>
@@ -48718,7 +48862,7 @@
         <v>1091302</v>
       </c>
       <c r="AB451" s="18" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="AC451" s="18">
         <v>1013</v>
@@ -48734,7 +48878,7 @@
       <c r="AH451" s="18"/>
       <c r="AI451" s="18"/>
     </row>
-    <row r="452" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="452" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C452" t="s">
         <v>1208</v>
       </c>
@@ -48807,7 +48951,7 @@
         <v>1091701</v>
       </c>
       <c r="AB452" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC452" s="18">
         <v>1017</v>
@@ -48823,7 +48967,7 @@
       <c r="AH452" s="18"/>
       <c r="AI452" s="18"/>
     </row>
-    <row r="453" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="453" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C453" t="s">
         <v>1210</v>
       </c>
@@ -48896,7 +49040,7 @@
         <v>1091701</v>
       </c>
       <c r="AB453" s="18" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="AC453" s="18">
         <v>1017</v>
@@ -48912,7 +49056,7 @@
       <c r="AH453" s="18"/>
       <c r="AI453" s="18"/>
     </row>
-    <row r="454" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="454" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C454" t="s">
         <v>1212</v>
       </c>
@@ -48995,7 +49139,7 @@
       <c r="AH454" s="18"/>
       <c r="AI454" s="18"/>
     </row>
-    <row r="455" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="455" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C455" t="s">
         <v>1214</v>
       </c>
@@ -49078,7 +49222,7 @@
       <c r="AH455" s="18"/>
       <c r="AI455" s="18"/>
     </row>
-    <row r="456" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="456" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C456" t="s">
         <v>1216</v>
       </c>
@@ -49161,7 +49305,7 @@
       <c r="AH456" s="18"/>
       <c r="AI456" s="18"/>
     </row>
-    <row r="457" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="457" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C457" t="s">
         <v>1218</v>
       </c>
@@ -49244,7 +49388,7 @@
       <c r="AH457" s="18"/>
       <c r="AI457" s="18"/>
     </row>
-    <row r="458" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="458" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C458" t="s">
         <v>1220</v>
       </c>
@@ -49327,7 +49471,7 @@
       <c r="AH458" s="18"/>
       <c r="AI458" s="18"/>
     </row>
-    <row r="459" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="459" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C459" t="s">
         <v>1222</v>
       </c>
@@ -49410,7 +49554,7 @@
       <c r="AH459" s="18"/>
       <c r="AI459" s="18"/>
     </row>
-    <row r="460" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="460" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C460" t="s">
         <v>1224</v>
       </c>
@@ -49493,7 +49637,7 @@
       <c r="AH460" s="18"/>
       <c r="AI460" s="18"/>
     </row>
-    <row r="461" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="461" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C461" t="s">
         <v>1226</v>
       </c>
@@ -49576,36 +49720,33 @@
       <c r="AH461" s="18"/>
       <c r="AI461" s="18"/>
     </row>
-    <row r="462" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A462" t="s">
-        <v>1323</v>
-      </c>
+    <row r="462" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C462" t="s">
-        <v>1324</v>
+        <v>1685</v>
       </c>
       <c r="D462" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E462" s="18">
-        <v>50001</v>
+        <v>40022</v>
       </c>
       <c r="F462" s="18">
-        <v>650001</v>
+        <v>620022</v>
       </c>
       <c r="G462" s="18">
-        <v>650002</v>
+        <v>630022</v>
       </c>
       <c r="H462" s="18">
-        <v>10410</v>
+        <v>10605</v>
       </c>
       <c r="I462" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J462" s="18">
         <v>4</v>
       </c>
       <c r="K462" s="18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L462" s="18">
         <v>5</v>
@@ -49627,35 +49768,35 @@
         <v>0</v>
       </c>
       <c r="S462" s="24" t="s">
-        <v>1441</v>
+        <v>1726</v>
       </c>
       <c r="T462" s="24" t="s">
-        <v>1329</v>
+        <v>1703</v>
       </c>
       <c r="U462" s="46" t="s">
-        <v>1327</v>
+        <v>1713</v>
       </c>
       <c r="V462" s="24">
         <v>101</v>
       </c>
       <c r="W462" s="18">
-        <v>10053</v>
+        <v>10057</v>
       </c>
       <c r="X462" s="18"/>
       <c r="Y462" s="18">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="Z462" s="18">
         <v>0</v>
       </c>
       <c r="AA462" s="18">
-        <v>1090201</v>
+        <v>1092101</v>
       </c>
       <c r="AB462" s="18" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="AC462" s="18">
-        <v>1002</v>
+        <v>1021</v>
       </c>
       <c r="AD462" s="18">
         <v>0</v>
@@ -49668,33 +49809,33 @@
       <c r="AH462" s="18"/>
       <c r="AI462" s="18"/>
     </row>
-    <row r="463" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="463" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C463" t="s">
-        <v>1325</v>
+        <v>1686</v>
       </c>
       <c r="D463" t="s">
-        <v>1202</v>
+        <v>264</v>
       </c>
       <c r="E463" s="18">
-        <v>50002</v>
+        <v>40023</v>
       </c>
       <c r="F463" s="18">
-        <v>650003</v>
+        <v>620023</v>
       </c>
       <c r="G463" s="18">
-        <v>650004</v>
-      </c>
-      <c r="H463" s="24" t="s">
-        <v>587</v>
+        <v>630023</v>
+      </c>
+      <c r="H463" s="18">
+        <v>10102</v>
       </c>
       <c r="I463" s="18">
         <v>1</v>
       </c>
       <c r="J463" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K463" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L463" s="18">
         <v>5</v>
@@ -49716,19 +49857,19 @@
         <v>0</v>
       </c>
       <c r="S463" s="24" t="s">
-        <v>1261</v>
+        <v>1698</v>
       </c>
       <c r="T463" s="24" t="s">
-        <v>1330</v>
+        <v>1704</v>
       </c>
       <c r="U463" s="46" t="s">
-        <v>1328</v>
+        <v>1714</v>
       </c>
       <c r="V463" s="24">
         <v>101</v>
       </c>
       <c r="W463" s="18">
-        <v>10006</v>
+        <v>10049</v>
       </c>
       <c r="X463" s="18"/>
       <c r="Y463" s="18">
@@ -49738,13 +49879,13 @@
         <v>0</v>
       </c>
       <c r="AA463" s="18">
-        <v>1091302</v>
+        <v>1090101</v>
       </c>
       <c r="AB463" s="18" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="AC463" s="18">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="AD463" s="18">
         <v>0</v>
@@ -49757,24 +49898,24 @@
       <c r="AH463" s="18"/>
       <c r="AI463" s="18"/>
     </row>
-    <row r="464" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="464" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C464" t="s">
-        <v>1326</v>
+        <v>1687</v>
       </c>
       <c r="D464" t="s">
-        <v>264</v>
+        <v>23</v>
       </c>
       <c r="E464" s="18">
-        <v>50003</v>
+        <v>40024</v>
       </c>
       <c r="F464" s="18">
-        <v>650005</v>
+        <v>620024</v>
       </c>
       <c r="G464" s="18">
-        <v>650006</v>
-      </c>
-      <c r="H464" s="18">
-        <v>10105</v>
+        <v>630024</v>
+      </c>
+      <c r="H464" s="24" t="s">
+        <v>1722</v>
       </c>
       <c r="I464" s="18">
         <v>1</v>
@@ -49783,7 +49924,7 @@
         <v>3</v>
       </c>
       <c r="K464" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L464" s="18">
         <v>5</v>
@@ -49805,35 +49946,35 @@
         <v>0</v>
       </c>
       <c r="S464" s="24" t="s">
-        <v>1442</v>
+        <v>1702</v>
       </c>
       <c r="T464" s="24" t="s">
-        <v>1331</v>
+        <v>1705</v>
       </c>
       <c r="U464" s="46" t="s">
-        <v>1332</v>
+        <v>1727</v>
       </c>
       <c r="V464" s="24">
         <v>101</v>
       </c>
       <c r="W464" s="18">
-        <v>10049</v>
+        <v>10051</v>
       </c>
       <c r="X464" s="18"/>
       <c r="Y464" s="18">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Z464" s="18">
         <v>0</v>
       </c>
       <c r="AA464" s="18">
-        <v>1090101</v>
+        <v>1092001</v>
       </c>
       <c r="AB464" s="18" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="AC464" s="18">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="AD464" s="18">
         <v>0</v>
@@ -49845,6 +49986,875 @@
       <c r="AG464" s="18"/>
       <c r="AH464" s="18"/>
       <c r="AI464" s="18"/>
+    </row>
+    <row r="465" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C465" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D465" t="s">
+        <v>24</v>
+      </c>
+      <c r="E465" s="18">
+        <v>40025</v>
+      </c>
+      <c r="F465" s="18">
+        <v>620025</v>
+      </c>
+      <c r="G465" s="18">
+        <v>630025</v>
+      </c>
+      <c r="H465" s="24" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I465" s="18">
+        <v>1</v>
+      </c>
+      <c r="J465" s="18">
+        <v>3</v>
+      </c>
+      <c r="K465" s="18">
+        <v>4</v>
+      </c>
+      <c r="L465" s="18">
+        <v>5</v>
+      </c>
+      <c r="M465" s="18"/>
+      <c r="N465" s="18">
+        <v>300</v>
+      </c>
+      <c r="O465" s="18">
+        <v>3</v>
+      </c>
+      <c r="P465" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q465" s="18">
+        <v>0</v>
+      </c>
+      <c r="R465" s="18">
+        <v>0</v>
+      </c>
+      <c r="S465" s="24" t="s">
+        <v>1699</v>
+      </c>
+      <c r="T465" s="24" t="s">
+        <v>1706</v>
+      </c>
+      <c r="U465" s="46" t="s">
+        <v>1715</v>
+      </c>
+      <c r="V465" s="24">
+        <v>101</v>
+      </c>
+      <c r="W465" s="18">
+        <v>10024</v>
+      </c>
+      <c r="X465" s="18"/>
+      <c r="Y465" s="18">
+        <v>800</v>
+      </c>
+      <c r="Z465" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA465" s="18">
+        <v>1090501</v>
+      </c>
+      <c r="AB465" s="18" t="s">
+        <v>1449</v>
+      </c>
+      <c r="AC465" s="18">
+        <v>1001</v>
+      </c>
+      <c r="AD465" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE465" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF465" s="18"/>
+      <c r="AG465" s="18"/>
+      <c r="AH465" s="18"/>
+      <c r="AI465" s="18"/>
+    </row>
+    <row r="466" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C466" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D466" t="s">
+        <v>24</v>
+      </c>
+      <c r="E466" s="18">
+        <v>40026</v>
+      </c>
+      <c r="F466" s="18">
+        <v>620026</v>
+      </c>
+      <c r="G466" s="18">
+        <v>630026</v>
+      </c>
+      <c r="H466" s="24" t="s">
+        <v>1723</v>
+      </c>
+      <c r="I466" s="18">
+        <v>1</v>
+      </c>
+      <c r="J466" s="18">
+        <v>3</v>
+      </c>
+      <c r="K466" s="18">
+        <v>4</v>
+      </c>
+      <c r="L466" s="18">
+        <v>5</v>
+      </c>
+      <c r="M466" s="18"/>
+      <c r="N466" s="18">
+        <v>300</v>
+      </c>
+      <c r="O466" s="18">
+        <v>3</v>
+      </c>
+      <c r="P466" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q466" s="18">
+        <v>0</v>
+      </c>
+      <c r="R466" s="18">
+        <v>0</v>
+      </c>
+      <c r="S466" s="24" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T466" s="24" t="s">
+        <v>1707</v>
+      </c>
+      <c r="U466" s="46" t="s">
+        <v>1716</v>
+      </c>
+      <c r="V466" s="24">
+        <v>101</v>
+      </c>
+      <c r="W466" s="18">
+        <v>10024</v>
+      </c>
+      <c r="X466" s="18"/>
+      <c r="Y466" s="18">
+        <v>800</v>
+      </c>
+      <c r="Z466" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA466" s="18">
+        <v>1090501</v>
+      </c>
+      <c r="AB466" s="18" t="s">
+        <v>1449</v>
+      </c>
+      <c r="AC466" s="18">
+        <v>1001</v>
+      </c>
+      <c r="AD466" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE466" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF466" s="18"/>
+      <c r="AG466" s="18"/>
+      <c r="AH466" s="18"/>
+      <c r="AI466" s="18"/>
+    </row>
+    <row r="467" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C467" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D467" t="s">
+        <v>24</v>
+      </c>
+      <c r="E467" s="18">
+        <v>40027</v>
+      </c>
+      <c r="F467" s="18">
+        <v>620027</v>
+      </c>
+      <c r="G467" s="18">
+        <v>630027</v>
+      </c>
+      <c r="H467" s="24" t="s">
+        <v>1724</v>
+      </c>
+      <c r="I467" s="18">
+        <v>1</v>
+      </c>
+      <c r="J467" s="18">
+        <v>3</v>
+      </c>
+      <c r="K467" s="18">
+        <v>4</v>
+      </c>
+      <c r="L467" s="18">
+        <v>5</v>
+      </c>
+      <c r="M467" s="18"/>
+      <c r="N467" s="18">
+        <v>300</v>
+      </c>
+      <c r="O467" s="18">
+        <v>3</v>
+      </c>
+      <c r="P467" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q467" s="18">
+        <v>0</v>
+      </c>
+      <c r="R467" s="18">
+        <v>0</v>
+      </c>
+      <c r="S467" s="24" t="s">
+        <v>1700</v>
+      </c>
+      <c r="T467" s="24" t="s">
+        <v>1708</v>
+      </c>
+      <c r="U467" s="46" t="s">
+        <v>1717</v>
+      </c>
+      <c r="V467" s="24">
+        <v>101</v>
+      </c>
+      <c r="W467" s="18">
+        <v>10024</v>
+      </c>
+      <c r="X467" s="18"/>
+      <c r="Y467" s="18">
+        <v>800</v>
+      </c>
+      <c r="Z467" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA467" s="18">
+        <v>1090501</v>
+      </c>
+      <c r="AB467" s="18" t="s">
+        <v>1449</v>
+      </c>
+      <c r="AC467" s="18">
+        <v>1001</v>
+      </c>
+      <c r="AD467" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE467" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF467" s="18"/>
+      <c r="AG467" s="18"/>
+      <c r="AH467" s="18"/>
+      <c r="AI467" s="18"/>
+    </row>
+    <row r="468" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C468" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D468" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E468" s="18">
+        <v>40028</v>
+      </c>
+      <c r="F468" s="18">
+        <v>620028</v>
+      </c>
+      <c r="G468" s="18">
+        <v>630028</v>
+      </c>
+      <c r="H468" s="24" t="s">
+        <v>1628</v>
+      </c>
+      <c r="I468" s="18">
+        <v>1</v>
+      </c>
+      <c r="J468" s="18">
+        <v>1</v>
+      </c>
+      <c r="K468" s="18">
+        <v>31</v>
+      </c>
+      <c r="L468" s="18">
+        <v>5</v>
+      </c>
+      <c r="M468" s="18"/>
+      <c r="N468" s="18">
+        <v>300</v>
+      </c>
+      <c r="O468" s="18">
+        <v>3</v>
+      </c>
+      <c r="P468" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q468" s="18">
+        <v>0</v>
+      </c>
+      <c r="R468" s="18">
+        <v>0</v>
+      </c>
+      <c r="S468" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="T468" s="24" t="s">
+        <v>1709</v>
+      </c>
+      <c r="U468" s="46" t="s">
+        <v>1718</v>
+      </c>
+      <c r="V468" s="24">
+        <v>101</v>
+      </c>
+      <c r="W468" s="18"/>
+      <c r="X468" s="18"/>
+      <c r="Y468" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z468" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA468" s="18"/>
+      <c r="AB468" s="18"/>
+      <c r="AC468" s="18">
+        <v>1026</v>
+      </c>
+      <c r="AD468" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE468" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF468" s="24"/>
+      <c r="AG468" s="18"/>
+      <c r="AH468" s="18"/>
+      <c r="AI468" s="18"/>
+    </row>
+    <row r="469" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C469" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E469" s="18">
+        <v>40029</v>
+      </c>
+      <c r="F469" s="18">
+        <v>620029</v>
+      </c>
+      <c r="G469" s="18">
+        <v>630029</v>
+      </c>
+      <c r="H469" s="24" t="s">
+        <v>769</v>
+      </c>
+      <c r="I469" s="18">
+        <v>1</v>
+      </c>
+      <c r="J469" s="18">
+        <v>1</v>
+      </c>
+      <c r="K469" s="18">
+        <v>31</v>
+      </c>
+      <c r="L469" s="18">
+        <v>5</v>
+      </c>
+      <c r="M469" s="18"/>
+      <c r="N469" s="18">
+        <v>300</v>
+      </c>
+      <c r="O469" s="18">
+        <v>3</v>
+      </c>
+      <c r="P469" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q469" s="18">
+        <v>0</v>
+      </c>
+      <c r="R469" s="18">
+        <v>0</v>
+      </c>
+      <c r="S469" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="T469" s="24" t="s">
+        <v>1710</v>
+      </c>
+      <c r="U469" s="46" t="s">
+        <v>1719</v>
+      </c>
+      <c r="V469" s="24">
+        <v>101</v>
+      </c>
+      <c r="W469" s="18"/>
+      <c r="X469" s="18"/>
+      <c r="Y469" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z469" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA469" s="18"/>
+      <c r="AB469" s="18"/>
+      <c r="AC469" s="18">
+        <v>1026</v>
+      </c>
+      <c r="AD469" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE469" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF469" s="24"/>
+      <c r="AG469" s="18"/>
+      <c r="AH469" s="18"/>
+      <c r="AI469" s="18"/>
+    </row>
+    <row r="470" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C470" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D470" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E470" s="18">
+        <v>40030</v>
+      </c>
+      <c r="F470" s="18">
+        <v>620030</v>
+      </c>
+      <c r="G470" s="18">
+        <v>630030</v>
+      </c>
+      <c r="H470" s="24" t="s">
+        <v>1421</v>
+      </c>
+      <c r="I470" s="18">
+        <v>1</v>
+      </c>
+      <c r="J470" s="18">
+        <v>1</v>
+      </c>
+      <c r="K470" s="18">
+        <v>31</v>
+      </c>
+      <c r="L470" s="18">
+        <v>5</v>
+      </c>
+      <c r="M470" s="18"/>
+      <c r="N470" s="18">
+        <v>300</v>
+      </c>
+      <c r="O470" s="18">
+        <v>3</v>
+      </c>
+      <c r="P470" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q470" s="18">
+        <v>0</v>
+      </c>
+      <c r="R470" s="18">
+        <v>0</v>
+      </c>
+      <c r="S470" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="T470" s="24" t="s">
+        <v>1711</v>
+      </c>
+      <c r="U470" s="46" t="s">
+        <v>1720</v>
+      </c>
+      <c r="V470" s="24">
+        <v>101</v>
+      </c>
+      <c r="W470" s="18"/>
+      <c r="X470" s="18"/>
+      <c r="Y470" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z470" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA470" s="18"/>
+      <c r="AB470" s="18"/>
+      <c r="AC470" s="18">
+        <v>1026</v>
+      </c>
+      <c r="AD470" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE470" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF470" s="24"/>
+      <c r="AG470" s="18"/>
+      <c r="AH470" s="18"/>
+      <c r="AI470" s="18"/>
+    </row>
+    <row r="471" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C471" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D471" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E471" s="18">
+        <v>40031</v>
+      </c>
+      <c r="F471" s="18">
+        <v>620031</v>
+      </c>
+      <c r="G471" s="18">
+        <v>630031</v>
+      </c>
+      <c r="H471" s="24" t="s">
+        <v>1725</v>
+      </c>
+      <c r="I471" s="18">
+        <v>1</v>
+      </c>
+      <c r="J471" s="18">
+        <v>1</v>
+      </c>
+      <c r="K471" s="18">
+        <v>31</v>
+      </c>
+      <c r="L471" s="18">
+        <v>5</v>
+      </c>
+      <c r="M471" s="18"/>
+      <c r="N471" s="18">
+        <v>300</v>
+      </c>
+      <c r="O471" s="18">
+        <v>3</v>
+      </c>
+      <c r="P471" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q471" s="18">
+        <v>0</v>
+      </c>
+      <c r="R471" s="18">
+        <v>0</v>
+      </c>
+      <c r="S471" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="T471" s="24" t="s">
+        <v>1712</v>
+      </c>
+      <c r="U471" s="46" t="s">
+        <v>1721</v>
+      </c>
+      <c r="V471" s="24">
+        <v>101</v>
+      </c>
+      <c r="W471" s="18"/>
+      <c r="X471" s="18"/>
+      <c r="Y471" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z471" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA471" s="18"/>
+      <c r="AB471" s="18"/>
+      <c r="AC471" s="18">
+        <v>1026</v>
+      </c>
+      <c r="AD471" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE471" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF471" s="24"/>
+      <c r="AG471" s="18"/>
+      <c r="AH471" s="18"/>
+      <c r="AI471" s="18"/>
+    </row>
+    <row r="472" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C472" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D472" t="s">
+        <v>25</v>
+      </c>
+      <c r="E472" s="18">
+        <v>50001</v>
+      </c>
+      <c r="F472" s="18">
+        <v>650001</v>
+      </c>
+      <c r="G472" s="18">
+        <v>650002</v>
+      </c>
+      <c r="H472" s="18">
+        <v>10410</v>
+      </c>
+      <c r="I472" s="18">
+        <v>1</v>
+      </c>
+      <c r="J472" s="18">
+        <v>4</v>
+      </c>
+      <c r="K472" s="18">
+        <v>5</v>
+      </c>
+      <c r="L472" s="18">
+        <v>5</v>
+      </c>
+      <c r="M472" s="18"/>
+      <c r="N472" s="18">
+        <v>300</v>
+      </c>
+      <c r="O472" s="18">
+        <v>3</v>
+      </c>
+      <c r="P472" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q472" s="18">
+        <v>0</v>
+      </c>
+      <c r="R472" s="18">
+        <v>0</v>
+      </c>
+      <c r="S472" s="24" t="s">
+        <v>1695</v>
+      </c>
+      <c r="T472" s="24" t="s">
+        <v>1329</v>
+      </c>
+      <c r="U472" s="46" t="s">
+        <v>1327</v>
+      </c>
+      <c r="V472" s="24">
+        <v>101</v>
+      </c>
+      <c r="W472" s="18">
+        <v>10053</v>
+      </c>
+      <c r="X472" s="18"/>
+      <c r="Y472" s="18">
+        <v>1300</v>
+      </c>
+      <c r="Z472" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA472" s="18">
+        <v>1090201</v>
+      </c>
+      <c r="AB472" s="18" t="s">
+        <v>1450</v>
+      </c>
+      <c r="AC472" s="18">
+        <v>1002</v>
+      </c>
+      <c r="AD472" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE472" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF472" s="24"/>
+      <c r="AG472" s="18"/>
+      <c r="AH472" s="18"/>
+      <c r="AI472" s="18"/>
+    </row>
+    <row r="473" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C473" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E473" s="18">
+        <v>50002</v>
+      </c>
+      <c r="F473" s="18">
+        <v>650003</v>
+      </c>
+      <c r="G473" s="18">
+        <v>650004</v>
+      </c>
+      <c r="H473" s="24" t="s">
+        <v>587</v>
+      </c>
+      <c r="I473" s="18">
+        <v>1</v>
+      </c>
+      <c r="J473" s="18">
+        <v>4</v>
+      </c>
+      <c r="K473" s="18">
+        <v>8</v>
+      </c>
+      <c r="L473" s="18">
+        <v>5</v>
+      </c>
+      <c r="M473" s="18"/>
+      <c r="N473" s="18">
+        <v>300</v>
+      </c>
+      <c r="O473" s="18">
+        <v>3</v>
+      </c>
+      <c r="P473" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q473" s="18">
+        <v>0</v>
+      </c>
+      <c r="R473" s="18">
+        <v>0</v>
+      </c>
+      <c r="S473" s="24" t="s">
+        <v>1696</v>
+      </c>
+      <c r="T473" s="24" t="s">
+        <v>1330</v>
+      </c>
+      <c r="U473" s="46" t="s">
+        <v>1328</v>
+      </c>
+      <c r="V473" s="24">
+        <v>101</v>
+      </c>
+      <c r="W473" s="18">
+        <v>10006</v>
+      </c>
+      <c r="X473" s="18"/>
+      <c r="Y473" s="18">
+        <v>1200</v>
+      </c>
+      <c r="Z473" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA473" s="18">
+        <v>1091302</v>
+      </c>
+      <c r="AB473" s="18" t="s">
+        <v>1451</v>
+      </c>
+      <c r="AC473" s="18">
+        <v>1013</v>
+      </c>
+      <c r="AD473" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE473" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF473" s="24"/>
+      <c r="AG473" s="18"/>
+      <c r="AH473" s="18"/>
+      <c r="AI473" s="18"/>
+    </row>
+    <row r="474" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C474" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D474" t="s">
+        <v>264</v>
+      </c>
+      <c r="E474" s="18">
+        <v>50003</v>
+      </c>
+      <c r="F474" s="18">
+        <v>650005</v>
+      </c>
+      <c r="G474" s="18">
+        <v>650006</v>
+      </c>
+      <c r="H474" s="18">
+        <v>10105</v>
+      </c>
+      <c r="I474" s="18">
+        <v>1</v>
+      </c>
+      <c r="J474" s="18">
+        <v>3</v>
+      </c>
+      <c r="K474" s="18">
+        <v>1</v>
+      </c>
+      <c r="L474" s="18">
+        <v>5</v>
+      </c>
+      <c r="M474" s="18"/>
+      <c r="N474" s="18">
+        <v>300</v>
+      </c>
+      <c r="O474" s="18">
+        <v>3</v>
+      </c>
+      <c r="P474" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q474" s="18">
+        <v>0</v>
+      </c>
+      <c r="R474" s="18">
+        <v>0</v>
+      </c>
+      <c r="S474" s="24" t="s">
+        <v>1697</v>
+      </c>
+      <c r="T474" s="24" t="s">
+        <v>1331</v>
+      </c>
+      <c r="U474" s="46" t="s">
+        <v>1332</v>
+      </c>
+      <c r="V474" s="24">
+        <v>101</v>
+      </c>
+      <c r="W474" s="18">
+        <v>10049</v>
+      </c>
+      <c r="X474" s="18"/>
+      <c r="Y474" s="18">
+        <v>1200</v>
+      </c>
+      <c r="Z474" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA474" s="18">
+        <v>1090101</v>
+      </c>
+      <c r="AB474" s="18" t="s">
+        <v>1448</v>
+      </c>
+      <c r="AC474" s="18">
+        <v>1001</v>
+      </c>
+      <c r="AD474" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE474" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF474" s="24"/>
+      <c r="AG474" s="18"/>
+      <c r="AH474" s="18"/>
+      <c r="AI474" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -49989,7 +50999,7 @@
         <v>353</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="I2" s="25" t="s">
         <v>369</v>
@@ -50575,7 +51585,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="C21" s="25">
         <v>17</v>
@@ -50590,16 +51600,16 @@
         <v>360</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="H21" s="26" t="s">
+        <v>1575</v>
+      </c>
+      <c r="I21" s="25" t="s">
         <v>1577</v>
       </c>
-      <c r="I21" s="25" t="s">
-        <v>1579</v>
-      </c>
       <c r="J21" s="26" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="25"/>
@@ -50607,7 +51617,7 @@
     </row>
     <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="C22" s="25">
         <v>18</v>
@@ -50622,16 +51632,16 @@
         <v>524</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="H22" s="25" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J22" s="26" t="s">
         <v>1580</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>1581</v>
-      </c>
-      <c r="J22" s="26" t="s">
-        <v>1582</v>
       </c>
       <c r="K22" s="25"/>
       <c r="L22" s="25"/>
@@ -50639,7 +51649,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="C23" s="25">
         <v>19</v>
@@ -50654,16 +51664,16 @@
         <v>524</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="H23" s="26" t="s">
+        <v>1582</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>1583</v>
+      </c>
+      <c r="J23" s="25" t="s">
         <v>1584</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>1585</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>1586</v>
       </c>
       <c r="K23" s="25"/>
       <c r="L23" s="25"/>
@@ -50671,7 +51681,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C24" s="25">
         <v>20</v>
@@ -50686,16 +51696,16 @@
         <v>524</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="J24" s="25" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
@@ -50703,7 +51713,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="C25" s="25">
         <v>21</v>
@@ -50718,16 +51728,16 @@
         <v>524</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="K25" s="25"/>
       <c r="L25" s="25"/>
@@ -50735,7 +51745,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="C26" s="25">
         <v>22</v>
@@ -50750,16 +51760,16 @@
         <v>524</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H26" s="26" t="s">
+        <v>1605</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J26" s="26" t="s">
         <v>1607</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>1608</v>
-      </c>
-      <c r="J26" s="26" t="s">
-        <v>1609</v>
       </c>
       <c r="K26" s="25"/>
       <c r="L26" s="25"/>
